--- a/artfynd/A 59607-2022 artfynd.xlsx
+++ b/artfynd/A 59607-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126190090</v>
       </c>
       <c r="B2" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126173594</v>
       </c>
       <c r="B3" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59607-2022 artfynd.xlsx
+++ b/artfynd/A 59607-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126190090</v>
       </c>
       <c r="B2" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126173594</v>
       </c>
       <c r="B3" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59607-2022 artfynd.xlsx
+++ b/artfynd/A 59607-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126190090</v>
       </c>
       <c r="B2" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126173594</v>
       </c>
       <c r="B3" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59607-2022 artfynd.xlsx
+++ b/artfynd/A 59607-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126190090</v>
       </c>
       <c r="B2" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126173594</v>
       </c>
       <c r="B3" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59607-2022 artfynd.xlsx
+++ b/artfynd/A 59607-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126190090</v>
       </c>
       <c r="B2" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126173594</v>
       </c>
       <c r="B3" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59607-2022 artfynd.xlsx
+++ b/artfynd/A 59607-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126190090</v>
       </c>
       <c r="B2" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126173594</v>
       </c>
       <c r="B3" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59607-2022 artfynd.xlsx
+++ b/artfynd/A 59607-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126190090</v>
+        <v>126173594</v>
       </c>
       <c r="B2" t="n">
-        <v>109185</v>
+        <v>110078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596103</v>
+        <v>596045</v>
       </c>
       <c r="R2" t="n">
-        <v>6553744</v>
+        <v>6553757</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>Vägslänt</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126173594</v>
+        <v>126190090</v>
       </c>
       <c r="B3" t="n">
-        <v>109185</v>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596045</v>
+        <v>596103</v>
       </c>
       <c r="R3" t="n">
-        <v>6553757</v>
+        <v>6553744</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Vägslänt</t>
+          <t>Lövskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -886,6 +886,113 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126173586</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grindatorp SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>596045</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6553757</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59607-2022 artfynd.xlsx
+++ b/artfynd/A 59607-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126173594</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126190090</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,8 +1008,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126173586</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>